--- a/day02/T.V_TV.xlsx
+++ b/day02/T.V_TV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\python-course-assignments\python-course-assignments\day02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9192717D-44F1-4E5B-A55E-77D9AF6781A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56D1CEE-51CE-4C47-A371-0AFC7D26E7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="16">
   <si>
     <t>cage</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>Sex</t>
+  </si>
+  <si>
+    <t>Error</t>
   </si>
   <si>
     <t>Non</t>
@@ -445,6 +448,9 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
@@ -454,7 +460,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <v>6.1</v>
@@ -466,7 +472,7 @@
         <v>129.30475000000001</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J2">
         <f>E2*E2*F2/2</f>
@@ -485,7 +491,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3">
         <v>4.97</v>
@@ -497,7 +503,7 @@
         <v>81.512969999999981</v>
       </c>
       <c r="H3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J3">
         <f t="shared" ref="J3:J42" si="0">E3*E3*F3/2</f>
@@ -516,7 +522,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4">
         <v>5.49</v>
@@ -528,7 +534,7 @@
         <v>108.50436000000001</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <f t="shared" si="0"/>
@@ -547,7 +553,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>5.41</v>
@@ -559,7 +565,7 @@
         <v>88.536002499999995</v>
       </c>
       <c r="H5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <f t="shared" si="0"/>
@@ -578,7 +584,7 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>4.3499999999999996</v>
@@ -590,7 +596,7 @@
         <v>66.701812499999988</v>
       </c>
       <c r="H6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
@@ -609,7 +615,7 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>5.7</v>
@@ -621,7 +627,7 @@
         <v>111.76560000000001</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
@@ -640,7 +646,7 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>4.5599999999999996</v>
@@ -652,7 +658,7 @@
         <v>53.75145599999999</v>
       </c>
       <c r="H8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <f t="shared" si="0"/>
@@ -671,7 +677,7 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9">
         <v>5.6</v>
@@ -683,7 +689,7 @@
         <v>116.50239999999999</v>
       </c>
       <c r="H9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <f t="shared" si="0"/>
@@ -702,7 +708,7 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10">
         <v>7.07</v>
@@ -714,7 +720,7 @@
         <v>192.94171399999999</v>
       </c>
       <c r="H10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <f t="shared" si="0"/>
@@ -733,7 +739,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11">
         <v>4.93</v>
@@ -745,7 +751,7 @@
         <v>62.463592999999989</v>
       </c>
       <c r="H11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <f t="shared" si="0"/>
@@ -764,7 +770,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12">
         <v>5.56</v>
@@ -776,7 +782,7 @@
         <v>137.720088</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12">
         <f t="shared" si="0"/>
@@ -795,7 +801,7 @@
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13">
         <v>5.31</v>
@@ -807,7 +813,7 @@
         <v>130.40696249999999</v>
       </c>
       <c r="H13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13">
         <f t="shared" si="0"/>
@@ -826,7 +832,7 @@
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14">
         <v>6.74</v>
@@ -838,7 +844,7 @@
         <v>181.483262</v>
       </c>
       <c r="H14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14">
         <f t="shared" si="0"/>
@@ -857,7 +863,7 @@
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15">
         <v>6.68</v>
@@ -869,7 +875,7 @@
         <v>201.24702400000001</v>
       </c>
       <c r="H15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15">
         <f t="shared" si="0"/>
@@ -888,7 +894,7 @@
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16">
         <v>5.36</v>
@@ -900,7 +906,7 @@
         <v>123.96822400000001</v>
       </c>
       <c r="H16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16">
         <f t="shared" si="0"/>
@@ -919,7 +925,7 @@
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17">
         <v>6.19</v>
@@ -931,7 +937,7 @@
         <v>145.40959950000001</v>
       </c>
       <c r="H17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17">
         <f t="shared" si="0"/>
@@ -950,7 +956,7 @@
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18">
         <v>5.6</v>
@@ -962,7 +968,7 @@
         <v>125.9104</v>
       </c>
       <c r="H18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18">
         <f t="shared" si="0"/>
@@ -981,7 +987,7 @@
         <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19">
         <v>4.7</v>
@@ -993,7 +999,7 @@
         <v>58.648950000000013</v>
       </c>
       <c r="H19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J19">
         <f t="shared" si="0"/>
@@ -1012,7 +1018,7 @@
         <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20">
         <v>5.4</v>
@@ -1024,7 +1030,7 @@
         <v>105.9966</v>
       </c>
       <c r="H20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20">
         <f t="shared" si="0"/>
@@ -1043,7 +1049,7 @@
         <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21">
         <v>5.61</v>
@@ -1055,7 +1061,7 @@
         <v>106.375698</v>
       </c>
       <c r="H21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <f t="shared" si="0"/>
@@ -1074,7 +1080,7 @@
         <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E22">
         <v>5.91</v>
@@ -1086,7 +1092,7 @@
         <v>116.31057300000001</v>
       </c>
       <c r="H22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <f t="shared" si="0"/>
@@ -1105,7 +1111,7 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E23">
         <v>7.13</v>
@@ -1117,7 +1123,7 @@
         <v>197.50135650000001</v>
       </c>
       <c r="H23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23">
         <f t="shared" si="0"/>
@@ -1136,7 +1142,7 @@
         <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24">
         <v>6.34</v>
@@ -1148,7 +1154,7 @@
         <v>144.50318200000001</v>
       </c>
       <c r="H24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J24">
         <f t="shared" si="0"/>
@@ -1167,7 +1173,7 @@
         <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25">
         <v>6.13</v>
@@ -1179,7 +1185,7 @@
         <v>151.9985605</v>
       </c>
       <c r="H25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J25">
         <f t="shared" si="0"/>
@@ -1198,7 +1204,7 @@
         <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26">
         <v>5.38</v>
@@ -1210,7 +1216,7 @@
         <v>89.582918000000006</v>
       </c>
       <c r="H26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J26">
         <f t="shared" si="0"/>
@@ -1229,7 +1235,7 @@
         <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E27">
         <v>5.41</v>
@@ -1241,7 +1247,7 @@
         <v>129.8040235</v>
       </c>
       <c r="H27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27">
         <f t="shared" si="0"/>
@@ -1260,7 +1266,7 @@
         <v>57</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E28">
         <v>5.8</v>
@@ -1272,7 +1278,7 @@
         <v>110.00279999999999</v>
       </c>
       <c r="H28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28">
         <f t="shared" si="0"/>
@@ -1291,7 +1297,7 @@
         <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E29">
         <v>4.68</v>
@@ -1303,7 +1309,7 @@
         <v>88.48569599999999</v>
       </c>
       <c r="H29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J29">
         <f t="shared" si="0"/>
@@ -1322,7 +1328,7 @@
         <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E30">
         <v>6.41</v>
@@ -1334,7 +1340,7 @@
         <v>180.17131850000001</v>
       </c>
       <c r="H30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J30">
         <f t="shared" si="0"/>
@@ -1353,7 +1359,7 @@
         <v>62</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31">
         <v>6.16</v>
@@ -1365,7 +1371,7 @@
         <v>122.75401599999999</v>
       </c>
       <c r="H31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J31">
         <f t="shared" si="0"/>
@@ -1384,7 +1390,7 @@
         <v>63</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E32">
         <v>5.63</v>
@@ -1396,7 +1402,7 @@
         <v>127.421538</v>
       </c>
       <c r="H32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J32">
         <f t="shared" si="0"/>
@@ -1415,7 +1421,7 @@
         <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E33">
         <v>5.19</v>
@@ -1427,7 +1433,7 @@
         <v>94.680391500000013</v>
       </c>
       <c r="H33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J33">
         <f t="shared" si="0"/>
@@ -1446,7 +1452,7 @@
         <v>66</v>
       </c>
       <c r="C34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E34">
         <v>5.61</v>
@@ -1458,7 +1464,7 @@
         <v>115.0305255</v>
       </c>
       <c r="H34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J34">
         <f t="shared" si="0"/>
@@ -1477,7 +1483,7 @@
         <v>67</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E35">
         <v>6.24</v>
@@ -1489,7 +1495,7 @@
         <v>150.299136</v>
       </c>
       <c r="H35" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J35">
         <f t="shared" si="0"/>
@@ -1508,7 +1514,7 @@
         <v>68</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E36">
         <v>5.49</v>
@@ -1520,7 +1526,7 @@
         <v>93.283609500000011</v>
       </c>
       <c r="H36" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J36">
         <f t="shared" si="0"/>
@@ -1539,7 +1545,7 @@
         <v>69</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E37">
         <v>5.73</v>
@@ -1551,7 +1557,7 @@
         <v>106.378596</v>
       </c>
       <c r="H37" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J37">
         <f t="shared" si="0"/>
@@ -1570,7 +1576,7 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E38">
         <v>5.42</v>
@@ -1582,7 +1588,7 @@
         <v>83.428975999999992</v>
       </c>
       <c r="H38" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J38">
         <f t="shared" si="0"/>
@@ -1601,7 +1607,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E39">
         <v>5.69</v>
@@ -1613,7 +1619,7 @@
         <v>121.5722555</v>
       </c>
       <c r="H39" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J39">
         <f t="shared" si="0"/>
@@ -1632,7 +1638,7 @@
         <v>74</v>
       </c>
       <c r="C40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E40">
         <v>6.42</v>
@@ -1644,7 +1650,7 @@
         <v>141.78441599999999</v>
       </c>
       <c r="H40" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J40">
         <f t="shared" si="0"/>
@@ -1663,7 +1669,7 @@
         <v>81</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E41">
         <v>4.9000000000000004</v>
@@ -1675,7 +1681,7 @@
         <v>64.346800000000016</v>
       </c>
       <c r="H41" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J41">
         <f t="shared" si="0"/>
@@ -1694,7 +1700,7 @@
         <v>82</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E42">
         <v>4.67</v>
@@ -1706,7 +1712,7 @@
         <v>73.605037499999995</v>
       </c>
       <c r="H42" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J42">
         <f t="shared" si="0"/>
